--- a/www/flightdata/xlsx/eoss-329.xlsx
+++ b/www/flightdata/xlsx/eoss-329.xlsx
@@ -4884,7 +4884,7 @@
         <v>28350.06</v>
       </c>
       <c r="I2">
-        <v>950</v>
+        <v>677</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
